--- a/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1826</t>
+          <t>1853</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10875</t>
+          <t>11044</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8886</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3910</t>
+          <t>3785</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15484</t>
+          <t>14739</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>683137</t>
+          <t>682968</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692186</t>
+          <t>692159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>680355</t>
+          <t>679465</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>687401</t>
+          <t>687403</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1366879</t>
+          <t>1367624</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1378453</t>
+          <t>1378578</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,73%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5564</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>21018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5510</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20066</t>
+          <t>19579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14937</t>
+          <t>14317</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34345</t>
+          <t>34870</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>941558</t>
+          <t>940782</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>956236</t>
+          <t>955699</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948327</t>
+          <t>948814</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>962883</t>
+          <t>962865</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1895848</t>
+          <t>1895323</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915256</t>
+          <t>1915876</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>987</t>
+          <t>980</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10026</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7446</t>
+          <t>7213</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22307</t>
+          <t>21765</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9934</t>
+          <t>9836</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27749</t>
+          <t>27629</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,03%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668483</t>
+          <t>668104</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677522</t>
+          <t>677529</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>661534</t>
+          <t>662076</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676395</t>
+          <t>676628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334601</t>
+          <t>1334721</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1352416</t>
+          <t>1352514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4120</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>17293</t>
+          <t>18553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6130</t>
+          <t>6725</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>21015</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>13390</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31861</t>
+          <t>33568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924929</t>
+          <t>923669</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938102</t>
+          <t>938026</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1017740</t>
+          <t>1017597</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1032482</t>
+          <t>1031887</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1948973</t>
+          <t>1947266</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1967444</t>
+          <t>1966648</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19763</t>
+          <t>20150</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41995</t>
+          <t>42995</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28622</t>
+          <t>28386</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53787</t>
+          <t>53962</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53688</t>
+          <t>54557</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87187</t>
+          <t>87362</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3234548</t>
+          <t>3233548</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3256780</t>
+          <t>3256393</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3325410</t>
+          <t>3325235</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3350575</t>
+          <t>3350811</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6568554</t>
+          <t>6568379</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6602053</t>
+          <t>6601184</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10626</t>
+          <t>10579</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29904</t>
+          <t>29592</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13782</t>
+          <t>13379</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32691</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>27972</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53779</t>
+          <t>54401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>673565</t>
+          <t>673877</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692843</t>
+          <t>692890</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,75%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>664359</t>
+          <t>665021</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>683268</t>
+          <t>683671</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,31%</t>
+          <t>95,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1346740</t>
+          <t>1346118</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1373854</t>
+          <t>1372547</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,0%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9215</t>
+          <t>9137</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26185</t>
+          <t>26623</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10966</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29357</t>
+          <t>28976</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24609</t>
+          <t>23810</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>48475</t>
+          <t>47446</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991762</t>
+          <t>991324</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008732</t>
+          <t>1008810</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1002827</t>
+          <t>1003208</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1021218</t>
+          <t>1021317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2001656</t>
+          <t>2002685</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2025522</t>
+          <t>2026321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3926</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>19133</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4056</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16857</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>28084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,83%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740820</t>
+          <t>738490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>754560</t>
+          <t>753697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760317</t>
+          <t>760848</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>772228</t>
+          <t>773118</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1506335</t>
+          <t>1506713</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524448</t>
+          <t>1524700</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34672</t>
+          <t>33119</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16133</t>
+          <t>16837</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38147</t>
+          <t>38240</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33778</t>
+          <t>33902</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62863</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>913067</t>
+          <t>914620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934271</t>
+          <t>934787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013754</t>
+          <t>1013661</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035768</t>
+          <t>1035064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936777</t>
+          <t>1937135</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965862</t>
+          <t>1965738</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>46068</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>81624</t>
+          <t>85110</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>58274</t>
+          <t>59306</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>95142</t>
+          <t>92986</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113673</t>
+          <t>114140</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>164089</t>
+          <t>162553</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3345155</t>
+          <t>3341669</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3380711</t>
+          <t>3377998</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3463167</t>
+          <t>3465323</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3500035</t>
+          <t>3499003</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6820999</t>
+          <t>6822535</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6871415</t>
+          <t>6870948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2853</t>
+          <t>3026</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3788</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8560</t>
+          <t>8458</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24477</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661492</t>
+          <t>660859</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671947</t>
+          <t>671774</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657747</t>
+          <t>657956</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669051</t>
+          <t>669142</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323162</t>
+          <t>1323229</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1339079</t>
+          <t>1339181</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6893</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23021</t>
+          <t>23771</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9266</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27098</t>
+          <t>28299</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19540</t>
+          <t>18902</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>43562</t>
+          <t>42576</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,06%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>999410</t>
+          <t>998660</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1015538</t>
+          <t>1016226</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1015815</t>
+          <t>1014614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1033647</t>
+          <t>1033522</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2021782</t>
+          <t>2022768</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2045804</t>
+          <t>2046442</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1063</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12214</t>
+          <t>11241</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3896</t>
+          <t>3129</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16770</t>
+          <t>16846</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7159</t>
+          <t>6790</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23279</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>747338</t>
+          <t>748311</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758489</t>
+          <t>758143</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768241</t>
+          <t>768165</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781115</t>
+          <t>781882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1521284</t>
+          <t>1520907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537404</t>
+          <t>1537773</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,56%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2893</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>13511</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>15218</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35750</t>
+          <t>36106</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20494</t>
+          <t>21439</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43230</t>
+          <t>44669</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923246</t>
+          <t>924056</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934697</t>
+          <t>934674</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1008029</t>
+          <t>1007673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028868</t>
+          <t>1028561</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1938116</t>
+          <t>1936677</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1960852</t>
+          <t>1959907</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22447</t>
+          <t>21114</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45701</t>
+          <t>46130</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>43518</t>
+          <t>42883</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74307</t>
+          <t>74139</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70551</t>
+          <t>71741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>109519</t>
+          <t>113052</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3348649</t>
+          <t>3348220</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3371903</t>
+          <t>3373236</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3470235</t>
+          <t>3470403</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3501024</t>
+          <t>3501659</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6829373</t>
+          <t>6825840</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6868341</t>
+          <t>6867151</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023</t>
+          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3374</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13945</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11774</t>
+          <t>11643</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25675</t>
+          <t>25633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17457</t>
+          <t>18079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34839</t>
+          <t>34608</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621944</t>
+          <t>621496</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>632067</t>
+          <t>631752</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699655</t>
+          <t>699697</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>713556</t>
+          <t>713687</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1325933</t>
+          <t>1326164</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1343315</t>
+          <t>1342693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,67%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7912</t>
+          <t>8406</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27714</t>
+          <t>28129</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19169</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34480</t>
+          <t>34534</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29639</t>
+          <t>28179</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58358</t>
+          <t>57613</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1165150</t>
+          <t>1164735</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1184952</t>
+          <t>1184458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>924171</t>
+          <t>924117</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939482</t>
+          <t>939416</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7085,7 +7085,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2093158</t>
+          <t>2093903</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2121877</t>
+          <t>2123337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13487</t>
+          <t>13584</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33534</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24280</t>
+          <t>23834</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>531579</t>
+          <t>570813</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>45372</t>
+          <t>44171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>704076</t>
+          <t>682057</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>41,64%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671146</t>
+          <t>671356</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691193</t>
+          <t>691096</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>401787</t>
+          <t>362553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909086</t>
+          <t>909532</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933970</t>
+          <t>955989</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1592674</t>
+          <t>1593875</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,3%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17198</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41823</t>
+          <t>42702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23460</t>
+          <t>23956</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45596</t>
+          <t>45527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46152</t>
+          <t>44668</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>79429</t>
+          <t>77759</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885008</t>
+          <t>884129</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>909633</t>
+          <t>908673</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1049336</t>
+          <t>1049405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1071472</t>
+          <t>1070976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1942334</t>
+          <t>1944004</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1975611</t>
+          <t>1977095</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>55572</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>96163</t>
+          <t>92622</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99266</t>
+          <t>99799</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>948285</t>
+          <t>932453</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,54%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166849</t>
+          <t>168822</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1081122</t>
+          <t>1039504</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,49%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3363654</t>
+          <t>3367195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3404245</t>
+          <t>3406402</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2763995</t>
+          <t>2779827</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3613014</t>
+          <t>3612481</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6090975</t>
+          <t>6132593</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7005248</t>
+          <t>7003275</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>85,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1853</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11044</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8886</t>
+          <t>8731</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>3785</t>
+          <t>3803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>15556</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682968</t>
+          <t>683151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692159</t>
+          <t>692115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>679465</t>
+          <t>679620</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1367624</t>
+          <t>1366807</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1378578</t>
+          <t>1378560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>6069</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21018</t>
+          <t>22010</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>19579</t>
+          <t>20551</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14317</t>
+          <t>14038</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>34948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>940782</t>
+          <t>939790</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>955699</t>
+          <t>955731</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>948814</t>
+          <t>947842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>962865</t>
+          <t>962609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1895323</t>
+          <t>1895245</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1915876</t>
+          <t>1916155</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>987</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10405</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7213</t>
+          <t>6355</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21765</t>
+          <t>20387</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9836</t>
+          <t>9692</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>27629</t>
+          <t>27255</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>668104</t>
+          <t>668221</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>677529</t>
+          <t>677522</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>662076</t>
+          <t>663454</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>676628</t>
+          <t>677486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1334721</t>
+          <t>1335095</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1352514</t>
+          <t>1352658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>4287</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18553</t>
+          <t>17949</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6725</t>
+          <t>6659</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21015</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14090</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>33568</t>
+          <t>33729</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>923669</t>
+          <t>924273</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>938026</t>
+          <t>937935</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1017597</t>
+          <t>1017739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1031887</t>
+          <t>1031953</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1947266</t>
+          <t>1947105</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1966648</t>
+          <t>1966744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20150</t>
+          <t>20555</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>44210</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28386</t>
+          <t>28524</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>53962</t>
+          <t>55457</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>54557</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87362</t>
+          <t>86909</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3233548</t>
+          <t>3232333</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3256393</t>
+          <t>3255988</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,82 +2233,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
+          <t>98,65%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,37%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3258</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>3339721</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>3323740</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3350673</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>98,83%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>98,36%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>99,16%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>6444</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>6586525</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>6568832</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>6602895</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>98,69%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,39%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>3339721</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>3325235</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3350811</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,83%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>99,16%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>6444</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6586525</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6568379</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>6601184</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>98,69%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10579</t>
+          <t>9745</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29592</t>
+          <t>29320</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>13379</t>
+          <t>12996</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>32029</t>
+          <t>31898</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>27972</t>
+          <t>26666</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54401</t>
+          <t>55161</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>673877</t>
+          <t>674149</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>692890</t>
+          <t>693724</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>665021</t>
+          <t>665152</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>683671</t>
+          <t>684054</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1346118</t>
+          <t>1345358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1372547</t>
+          <t>1373853</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,1%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9137</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26623</t>
+          <t>26496</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>10687</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28976</t>
+          <t>28058</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>23810</t>
+          <t>24106</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>47446</t>
+          <t>47667</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>991324</t>
+          <t>991451</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1008810</t>
+          <t>1008686</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1003208</t>
+          <t>1004126</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1021317</t>
+          <t>1021497</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2002685</t>
+          <t>2002464</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2026321</t>
+          <t>2026025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,82%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19133</t>
+          <t>18475</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>16340</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>28084</t>
+          <t>28131</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>738490</t>
+          <t>739148</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753697</t>
+          <t>753696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>760848</t>
+          <t>760834</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>773118</t>
+          <t>773087</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1506713</t>
+          <t>1506666</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1524700</t>
+          <t>1524751</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>13283</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33119</t>
+          <t>32901</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38240</t>
+          <t>37385</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33902</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>62102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>914620</t>
+          <t>914838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934787</t>
+          <t>934456</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1013661</t>
+          <t>1014516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1035064</t>
+          <t>1035719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1937135</t>
+          <t>1937538</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1965738</t>
+          <t>1965581</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>48481</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>85110</t>
+          <t>83120</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>59306</t>
+          <t>58689</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>92986</t>
+          <t>93319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114140</t>
+          <t>114989</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>162553</t>
+          <t>163756</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3341669</t>
+          <t>3343659</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3377998</t>
+          <t>3378298</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3465323</t>
+          <t>3464990</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3499003</t>
+          <t>3499620</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6822535</t>
+          <t>6821332</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6870948</t>
+          <t>6870099</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3026</t>
+          <t>2884</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,7 +4642,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3697</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14883</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>8458</t>
+          <t>8851</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>24410</t>
+          <t>25182</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660859</t>
+          <t>660853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>671774</t>
+          <t>671916</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>657956</t>
+          <t>657497</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>669142</t>
+          <t>669116</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1323229</t>
+          <t>1322457</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1339181</t>
+          <t>1338788</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6268</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23771</t>
+          <t>22229</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9391</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28299</t>
+          <t>26174</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>18902</t>
+          <t>19893</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>42576</t>
+          <t>43564</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998660</t>
+          <t>1000202</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1016226</t>
+          <t>1016163</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1014614</t>
+          <t>1016739</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1033522</t>
+          <t>1033155</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2022768</t>
+          <t>2021780</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2046442</t>
+          <t>2045451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1409</t>
+          <t>1061</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11829</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>4088</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16846</t>
+          <t>16727</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6790</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23656</t>
+          <t>22961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>748311</t>
+          <t>747723</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>758143</t>
+          <t>758491</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>768165</t>
+          <t>768284</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>781882</t>
+          <t>780923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1520907</t>
+          <t>1521602</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1537773</t>
+          <t>1537491</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,56%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2893</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15218</t>
+          <t>15196</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>36106</t>
+          <t>35929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21439</t>
+          <t>20795</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44669</t>
+          <t>44105</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>924056</t>
+          <t>922532</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>934674</t>
+          <t>933817</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1007673</t>
+          <t>1007850</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1028561</t>
+          <t>1028583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,54%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1936677</t>
+          <t>1937241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1959907</t>
+          <t>1960551</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>21114</t>
+          <t>21819</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>46130</t>
+          <t>44714</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42883</t>
+          <t>42859</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>73940</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>71741</t>
+          <t>71447</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>113052</t>
+          <t>109788</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,58%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3348220</t>
+          <t>3349636</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3373236</t>
+          <t>3372531</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3470403</t>
+          <t>3470602</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3501659</t>
+          <t>3501683</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6825840</t>
+          <t>6829104</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6867151</t>
+          <t>6867445</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7254</t>
+          <t>7368</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13945</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>17439</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11643</t>
+          <t>12872</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>25633</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>24693</t>
+          <t>26331</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18079</t>
+          <t>18109</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>34608</t>
+          <t>35620</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>628187</t>
+          <t>683342</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>621496</t>
+          <t>676524</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>631752</t>
+          <t>686938</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>707891</t>
+          <t>715217</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>699697</t>
+          <t>706754</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>713687</t>
+          <t>721308</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1336079</t>
+          <t>1398558</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1326164</t>
+          <t>1389269</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1342693</t>
+          <t>1406780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,73%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>725330</t>
+          <t>734180</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1360772</t>
+          <t>1424889</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>17137</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8406</t>
+          <t>12272</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28129</t>
+          <t>31515</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,22 +6947,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26287</t>
+          <t>29737</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19235</t>
+          <t>21568</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34534</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>43424</t>
+          <t>49724</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28179</t>
+          <t>38366</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>57613</t>
+          <t>64526</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,04%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1175727</t>
+          <t>1028931</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1164735</t>
+          <t>1017402</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1184458</t>
+          <t>1036645</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,64%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,27 +7060,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>932364</t>
+          <t>1041737</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>924117</t>
+          <t>1031671</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>939416</t>
+          <t>1049906</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2108092</t>
+          <t>2070667</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2093903</t>
+          <t>2055865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2123337</t>
+          <t>2082025</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958651</t>
+          <t>1071474</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2151516</t>
+          <t>2120391</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>21645</t>
+          <t>24730</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13584</t>
+          <t>16053</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33324</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>227057</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>20131</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>570813</t>
+          <t>43305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,16%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>248702</t>
+          <t>53415</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44171</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>682057</t>
+          <t>71367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,64%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>683035</t>
+          <t>778343</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>671356</t>
+          <t>765045</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>691096</t>
+          <t>787020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>706309</t>
+          <t>783574</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>362553</t>
+          <t>768954</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>909532</t>
+          <t>792128</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,84%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1389344</t>
+          <t>1561917</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>955989</t>
+          <t>1543965</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1593875</t>
+          <t>1575357</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,53%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>26949</t>
+          <t>29014</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18158</t>
+          <t>19134</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42702</t>
+          <t>43449</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>33445</t>
+          <t>36774</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>27680</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>45527</t>
+          <t>47432</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>60394</t>
+          <t>65788</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44668</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77759</t>
+          <t>82176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>899882</t>
+          <t>961048</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>884129</t>
+          <t>946613</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>908673</t>
+          <t>970928</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1061487</t>
+          <t>1082267</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1049405</t>
+          <t>1071609</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1070976</t>
+          <t>1091361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1961369</t>
+          <t>2043316</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1944004</t>
+          <t>2026928</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1977095</t>
+          <t>2056578</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,51%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1094932</t>
+          <t>1119041</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2021763</t>
+          <t>2109104</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>72985</t>
+          <t>81098</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>53415</t>
+          <t>64472</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92622</t>
+          <t>102248</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,67 +7976,67 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>304229</t>
+          <t>114160</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>99799</t>
+          <t>97053</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>932453</t>
+          <t>135221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,62%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>195258</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>170301</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>223138</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>25,12%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>377213</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>168822</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1039504</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,49%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3386832</t>
+          <t>3451664</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3367195</t>
+          <t>3430514</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3406402</t>
+          <t>3468290</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,67 +8089,67 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3408051</t>
+          <t>3622794</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2779827</t>
+          <t>3601733</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3612481</t>
+          <t>3639901</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>8501</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>7074458</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>7046578</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>7099415</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
           <t>97,31%</t>
         </is>
       </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>8501</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>6794884</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>6132593</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>7003275</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,51%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,66%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3459817</t>
+          <t>3532762</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3712280</t>
+          <t>3736954</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7172097</t>
+          <t>7269716</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">

--- a/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_psíq_R-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según si tienen personas con limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
+          <t>Población según si convive con personas con alguna limitación por discapacidad psíquica en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
